--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Keimzahl beschreibt die quantitative Bestimmung lebensfähiger Mikroorganismen in einer Probe als koloniebildende Einheiten pro Volumen oder Masse.</t>
+    <t>Keimzahl beschreibt die quantitative Bestimmung lebensfähiger Mikroorganismen in einer Probe als koloniebildende Einheiten je Volumen, je Masse oder als Anzahl je Probe.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1874,7 +1874,7 @@
     <t>Observation.value[x].code</t>
   </si>
   <si>
-    <t>Coded form of the unit</t>
+    <t>Bei Probenmaterialien ohne Volumen- oder Massenbezug, etwa Katheterspitzen, wird die nennerlose Einheit [CFU] verwendet; die Bezugsgröße steht in Specimen.type.</t>
   </si>
   <si>
     <t>A computer processable form of the unit in some unit representation system.</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1874,7 +1874,7 @@
     <t>Observation.value[x].code</t>
   </si>
   <si>
-    <t>Bei Probenmaterialien ohne Volumen- oder Massenbezug, etwa Katheterspitzen, wird die nennerlose Einheit [CFU] verwendet; die Bezugsgröße steht in Specimen.type.</t>
+    <t>Bevorzugt eine Einheit MIT der KBE-Annotation: [CFU]/mL je Volumen, [CFU]/g je Masse, [CFU] je Probe. Die unannotierten Formen /mL, /g und 1 sagen weniger — /mL heisst in UCUM woertlich 'pro Milliliter' und nicht, WAS pro Milliliter, und 1 ist die dimensionslose Eins. Sie bleiben zulaessig, weil sie bis 2025.0.2 die einzige Moeglichkeit waren; der Migrationspfad ist mechanisch. Bei Probenmaterialien ohne Volumen- oder Massenbezug, etwa Katheterspitzen, wird [CFU] verwendet und die Bezugsgroesse steht in Specimen.type.</t>
   </si>
   <si>
     <t>A computer processable form of the unit in some unit representation system.</t>
@@ -2129,7 +2129,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-pr-mikrobio-keimzahl.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
